--- a/release_notes/MTX/MTX_17.0_vs_16.3.xlsx
+++ b/release_notes/MTX/MTX_17.0_vs_16.3.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Readme" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="New Terms" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Term Name Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Existing Terms Changes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="master Reportability" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="legis Reportability" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="report Reportability" sheetId="6" state="visible" r:id="rId6"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -466,14 +466,10 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Term Name Changes Spreadsheet</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+          <t>New Terms Spreadsheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -490,36 +486,36 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Change</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Either a Scope Note change or a Name change</t>
+          <t>The commonly accepted name of the term added to the catalogue</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Old Value</t>
+          <t>Scope Note</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The value of the term in the previous version</t>
+          <t>A brief desciption of the added term</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>New Value</t>
+          <t>masterParentCode</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>The value of the term in the current version</t>
+          <t>The term code of the parent term</t>
         </is>
       </c>
     </row>
@@ -530,7 +526,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>New Terms Spreadsheet</t>
+          <t>Existing Terms Changes Spreadsheet</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr"/>
@@ -550,106 +546,142 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Change</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The commonly accepted name of the term added to the catalogue</t>
+          <t>Either a Scope Note change or a Name change</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>Old Value</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A brief desciption of the added term</t>
+          <t>The value of the term in the previous version</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>masterParentCode</t>
+          <t>New Value</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>The term code of the parent term</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>masterReportable</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Indicates whether the term is reportable (1) in the hierarchy or not (0).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="10" customHeight="1">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>{hierarchy_name} Reportability Spreadsheets</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
+          <t>The value of the term in the current version</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="10" customHeight="1">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Deprecated Terms Spreadsheet</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>The uniquely identifying term code for the catalogue</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The uniquely identifying term code for the catalogue</t>
+          <t>The commonly accepted name of the term in the catalogue</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Scope Note</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>A brief desciption of the term</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="10" customHeight="1">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>{hierarchy_name} Reportability Spreadsheets</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>The uniquely identifying term code for the catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>The common name of added or changed term</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Reportability Old</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>The previous reportability value of the term, can be either empty, 0 or 1. Empty indicates that the term is newly added to the hierarchy. Whereas the value 0 indicates that the term is not reportable and the value 1 indicates that the term is reportable within the hierarchy</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Reportability New</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>The new reportability value of the term, indicates that the term is either not reportable (0) or reportable (1) within the given hierarchy</t>
         </is>
@@ -666,14 +698,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,11 +728,6 @@
           <t>masterParentCode</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>masterReportable</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -724,9 +750,6 @@
           <t>A0C8K</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -749,183 +772,159 @@
           <t>A05QP</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A1B3K</t>
+          <t>A1B3G</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bird under 12 weeks old </t>
+          <t>FA-01.10 Milk-based drinks and similar products intended for young children</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Under 12 weeks old poultry</t>
+          <t>Descriptor from the classification defined in the food additives legislation (Regulation (EC) No 1333/2008)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A0C8K</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
+          <t>A0C5T</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A1B3S</t>
+          <t>A1B3K</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inca nut (as plant)</t>
+          <t xml:space="preserve">Bird under 12 weeks old </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Live plant organism of the taxonomic species Plukenetia volubilis. The plant is commonly known as Inca nut or Mountain peanut or Sacha inchi. The plant is a member of the family Euphorbiaceae. The part considered is by default the whole living organism.£https://en.wikipedia.org/wiki/Plukenetia_volubilis£https://www.worldfloraonline.org/taxon/wfo-0000279052</t>
+          <t>Under 12 weeks old poultry</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A05QP</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
+          <t>A0C8K</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A1B3X</t>
+          <t>A1B3L</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kluyveromyces lactis (as organism)</t>
+          <t>Bird over 12 weeks old</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Live organism of the taxonomic group Kluyveromyces lactis (Family = Saccharomycetaceae) (Order = Saccharomycetales). The part considered is by default the whole living organism.£https://en.wikipedia.org/wiki/Kluyveromyces_lactis</t>
+          <t>Over 12 weeks old poultry</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A0CPG</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
+          <t>A0C8K</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A1B4C</t>
+          <t>A1B3R</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mouse-eared bat (as animal)</t>
+          <t>Kajime seaweed (as organism)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Live animal of the taxonomic genus Myotis sp. The animals are commonly known Mouse-eared bat. The part considered is by default the whole living animal. £https://en.wikipedia.org/wiki/Mouse-eared_bat</t>
+          <t>Live organism of the taxonomic group Ecklonia cava. The organisms are commonly known as Kajime seaweed. The part considered is by default the whole living organism.£https://en.wikipedia.org/wiki/Ecklonia_cava</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A16CG</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
+          <t>A05MQ</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A1B3G</t>
+          <t>A1B3S</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FA-01.10 Milk-based drinks and similar products intended for young children</t>
+          <t>Inca nut (as plant)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Descriptor from the classification defined in the food additives legislation (Regulation (EC) No 1333/2008)</t>
+          <t>Live plant organism of the taxonomic species Plukenetia volubilis. The plant is commonly known as Inca nut or Mountain peanut or Sacha inchi. The plant is a member of the family Euphorbiaceae. The part considered is by default the whole living organism.£https://en.wikipedia.org/wiki/Plukenetia_volubilis£https://www.worldfloraonline.org/taxon/wfo-0000279052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A0C5T</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
+          <t>A05QP</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A1B3L</t>
+          <t>A1B3X</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bird over 12 weeks old</t>
+          <t>Kluyveromyces lactis (as organism)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Over 12 weeks old poultry</t>
+          <t>Live organism of the taxonomic group Kluyveromyces lactis (Family = Saccharomycetaceae) (Order = Saccharomycetales). The part considered is by default the whole living organism.£https://en.wikipedia.org/wiki/Kluyveromyces_lactis</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A0C8K</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
+          <t>A0CPG</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A1B3R</t>
+          <t>A1B4C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kajime seaweed (as organism)</t>
+          <t>Mouse-eared bat (as animal)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Live organism of the taxonomic group Ecklonia cava. The organisms are commonly known as Kajime seaweed. The part considered is by default the whole living organism.£https://en.wikipedia.org/wiki/Ecklonia_cava</t>
+          <t>Live animal of the taxonomic genus Myotis sp. The animals are commonly known Mouse-eared bat. The part considered is by default the whole living animal. £https://en.wikipedia.org/wiki/Mouse-eared_bat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A05MQ</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
+          <t>A16CG</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -949,9 +948,6 @@
           <t>A1B4C</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -974,108 +970,93 @@
           <t>A0C8K</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A1B3P</t>
+          <t>A1B3D</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ashitaba (as plant)</t>
+          <t>FA-18.1 Processed foods not covered by categories 18.2 and 18.3, excluding foods for infants and young children</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Live plant organism of the taxonomic group Angelica keiskei. The plant is a member of the family Apiaceae. The plant is commonly known as Ashitaba. The part considered is by default the whole living organism. £https://en.wikipedia.org/wiki/Ashitaba£https://www.worldfloraonline.org/taxon/wfo-0000536243</t>
+          <t>Descriptor from the classification defined in the food additives legislation (Regulation (EC) No 1333/2008)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A16MN</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
+          <t>A0C13</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A1B4B</t>
+          <t>A1B3O</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Common bent-wing bat (as animal)</t>
+          <t>Tallow tree (as plant)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Live animal of the taxonomic species Miniopterus schreibersii. The animals are commonly known Common bent-wing bat. The part considered is by default the whole living animal. £https://en.wikipedia.org/wiki/Common_bent-wing_bat</t>
+          <t>Live plant organism of the taxonomic group Allanblackia floribunda. The plant is a member of the family Clusiaceae. The plant is commonly known as Tallow tree. The part considered is by default the whole living organism. £https://en.wikipedia.org/wiki/Allanblackia_floribunda£https://www.worldfloraonline.org/taxon/wfo-0000525979</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A16CG</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
+          <t>A05QP</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A1B3D</t>
+          <t>A1B3P</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FA-18.1 Processed foods not covered by categories 18.2 and 18.3, excluding foods for infants and young children</t>
+          <t>Ashitaba (as plant)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Descriptor from the classification defined in the food additives legislation (Regulation (EC) No 1333/2008)</t>
+          <t>Live plant organism of the taxonomic group Angelica keiskei. The plant is a member of the family Apiaceae. The plant is commonly known as Ashitaba. The part considered is by default the whole living organism. £https://en.wikipedia.org/wiki/Ashitaba£https://www.worldfloraonline.org/taxon/wfo-0000536243</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A0C13</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
+          <t>A16MN</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A1B3O</t>
+          <t>A1B4B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tallow tree (as plant)</t>
+          <t>Common bent-wing bat (as animal)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Live plant organism of the taxonomic group Allanblackia floribunda. The plant is a member of the family Clusiaceae. The plant is commonly known as Tallow tree. The part considered is by default the whole living organism. £https://en.wikipedia.org/wiki/Allanblackia_floribunda£https://www.worldfloraonline.org/taxon/wfo-0000525979</t>
+          <t>Live animal of the taxonomic species Miniopterus schreibersii. The animals are commonly known Common bent-wing bat. The part considered is by default the whole living animal. £https://en.wikipedia.org/wiki/Common_bent-wing_bat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A05QP</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
+          <t>A16CG</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1099,9 +1080,6 @@
           <t>A05YP</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1124,9 +1102,6 @@
           <t>A05DY</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1149,9 +1124,6 @@
           <t>A05DY</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1174,9 +1146,6 @@
           <t>A03LB</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1199,9 +1168,6 @@
           <t>A16CG</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1224,9 +1190,6 @@
           <t>A056H</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1249,9 +1212,6 @@
           <t>A0C13</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1274,9 +1234,6 @@
           <t>A0C13</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1299,9 +1256,6 @@
           <t>A00LM</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1324,9 +1278,6 @@
           <t>A00ZA</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1349,9 +1300,6 @@
           <t>A047S</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1374,9 +1322,6 @@
           <t>A05YP</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1398,9 +1343,6 @@
         <is>
           <t>A16CG</t>
         </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1414,11 +1356,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1448,51 +1390,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A00EK</t>
+          <t>A048T</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>ScopeNote</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The group includes any type of Muesli plain, which is based only on cereals (i.e. without other major ingredients). The part consumed/analysed is by default the whole or a portion of it representing the observed heterogeneity.£https://www.google.co.uk/search?tbm=isch&amp;q=Muesli+plain</t>
+          <t>The group includes any type of Processing aids, i.e. substances intentionally used to process raw materials that are not present or are present at only insignificant levels in the finished food. The part consumed/analysed is by default the whole marketed unit or a homogeneous representative portion.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The group includes any type of Muesli plain, which is based only on cereals (i.e. without other major ingredients). When the term is accompanied by baking facet descriptors, it can be used to code granola. The part consumed/analysed is by default the whole or a portion of it representing the observed heterogeneity.£https://www.google.co.uk/search?tbm=isch&amp;q=Muesli+plain</t>
+          <t>The group includes any type of Processing aids, i.e. substances intentionally used to process raw materials that are not present or are present at only insignificant levels in the finished food. For example, pre-mixes used for the preparation of ice cream are included. The part consumed/analysed is by default the whole marketed unit or a homogeneous representative portion.£https://en.wikipedia.org/wiki/Processing_aid</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A00EL</t>
+          <t>A03RL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>implicitFacets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The group includes any type of Mixed breakfast cereals, including mixed muesli, usually made by cereal grains mixed with other ingredients, like raisins, chocolate, nuts and dried fruit. All the characterising ingredients should be reported with additional facet descriptors. The part consumed/analysed is by default the whole or a portion of it representing the observed heterogeneity.£https://www.google.co.uk/search?tbm=isch&amp;q=muesli with mixed ingredients</t>
+          <t>F02.A06FM$F33.A0C27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The group includes any type of Mixed breakfast cereals, including mixed muesli, usually made by cereal grains mixed with other ingredients, like raisins, chocolate, nuts and dried fruit. All the characterising ingredients should be reported with additional facet descriptors. Also, when the term is accompanied by baking facet descriptors, it can be used to code granola. The part consumed/analysed is by default the whole or a portion of it representing the observed heterogeneity.£https://www.google.co.uk/search?tbm=isch&amp;q=muesli with mixed ingredients</t>
+          <t>F02.A06FM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A00MB</t>
+          <t>A0C24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1502,85 +1444,85 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Radish leaves</t>
+          <t>FA-13.1.5.2 Dietary foods for babies and young children for special medical purposes as defined in Directive 1999/21/EC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Large radish leaves</t>
+          <t>FA-13.1.5.2 Foods for special medical purposes, as defined by Regulation (EU) No 609/2013, intended for infants as from four months of age and for young children</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A00MB</t>
+          <t>A0C2A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leaves from the plant classified under the species Raphanus sativus L., commonly known as Radish leaves. The part consumed/analysed is not specified. When relevant, information on the part consumed/analysed has to be reported with additional facet descriptors. In case of data collections related to legislations, the default part consumed/analysed is the one defined in the applicable legislation.£https://en.wikipedia.org/wiki/Raphanus_sativus£https://www.google.co.uk/search?tbm=isch&amp;q=Radish+leaves+</t>
+          <t>FA-13.1.1 Infant formulae as defined by Commission Directive 2006/141/EC ( 1 )</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Leaves from the plant classified under the species Raphanus sativus L., commonly known as Large radish leaves. The part consumed/analysed is not specified. When relevant, information on the part consumed/analysed has to be reported with additional facet descriptors. In case of data collections related to legislations, the default part consumed/analysed is the one defined in the applicable legislation.£https://en.wikipedia.org/wiki/Raphanus_sativus£https://www.google.co.uk/search?tbm=isch&amp;q=Radish+leaves+</t>
+          <t>FA-13.1.1 Infant formulae as defined by Regulation (EU) No 609/2013</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A02KC</t>
+          <t>A0C2C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The group includes any type of Fish fingers, breaded. The part consumed/analysed is by default the whole, or a portion representing the heterogeneity observed in the product. When relevant, information on the part consumed/analysed has to be reported with additional facet descriptors.£https://en.wikipedia.org/wiki/Fish_fingers£https://www.google.co.uk/search?tbm=isch&amp;q=Fish fingers, breaded</t>
+          <t>FA-13. Foods intended for particular nutritional uses as defined by Directive 2009/ 39/EC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The group includes any type of Fish fingers, breaded, including fish fillet. The part consumed/analysed is by default the whole, or a portion representing the heterogeneity observed in the product. When relevant, information on the part consumed/analysed has to be reported with additional facet descriptors.£https://en.wikipedia.org/wiki/Fish_fingers£https://www.google.co.uk/search?tbm=isch&amp;q=Fish fingers, breaded</t>
+          <t>FA-13. Foods intended for specific groups as defined by Regulation (EU) No 609/2013</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A048T</t>
+          <t>A03KK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>implicitFacets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The group includes any type of Processing aids, i.e. substances intentionally used to process raw materials that are not present or are present at only insignificant levels in the finished food. The part consumed/analysed is by default the whole marketed unit or a homogeneous representative portion.</t>
+          <t>F04.A03DK$F04.A03GN$F04.A03DM$F28.A07MK$F33.A0C1R</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The group includes any type of Processing aids, i.e. substances intentionally used to process raw materials that are not present or are present at only insignificant levels in the finished food. For example, pre-mixes used for the preparation of ice cream are included. The part consumed/analysed is by default the whole marketed unit or a homogeneous representative portion.£https://en.wikipedia.org/wiki/Processing_aid</t>
+          <t>F04.A03GN$F04.A03DM$F28.A07MK$F33.A0C1R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A0C13</t>
+          <t>A16EA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1590,261 +1532,257 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FA-18. Processed foods not covered by categories 1 to 17, excluding foods for infants and young children</t>
+          <t>Shrew (as animal)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FA-18. Processed foods not covered by categories 1 to 17</t>
+          <t>Soricidae (as animal)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A0C22</t>
+          <t>A16EA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>ScopeNote</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FA-13.3 Dietary foods for weight control diets intended to replace total daily food intake or an individual meal (the whole or part of the total daily diet)</t>
+          <t>Live animal of the taxonomic subfamilies Crocidurinae, Myosoricinae and Soricinae (in Soricidae family and in Eulipotyphla order). The animals are commonly known as Shrew or Shrew mouse (which is not a rodent and not a mole). The part considered is by default the whole living animal.£https://en.wikipedia.org/wiki/Shrew</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FA-13.3 Total diet replacement for weight control food as defined by Regulation (EU) No 609/2013</t>
+          <t>Live animal of the taxonomic family Soricidae (Eulipotyphla order). The animals are commonly known as Shrew or Shrew mouse (which is not a rodent and not a mole). The part considered is by default the whole living animal.£https://en.wikipedia.org/wiki/Shrew</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A0C23</t>
+          <t>A16EA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>scientificNames</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FA-13.2 Dietary foods for special medical purposes defined in Directive 1999/21/EC (excluding products from food category 13.1.5)</t>
+          <t>Soricidae(family)$Crocidurinae subfamily$Myosoricinae subfamily$Soricinae subfamily</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FA-13.2 Foods for special medical purposes as defined by Regulation (EU) No 609/2013 (excluding products from food category 13.1.5)</t>
+          <t>Soricidae (family)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A0C24</t>
+          <t>A16EA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>commonNames</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FA-13.1.5.2 Dietary foods for babies and young children for special medical purposes as defined in Directive 1999/21/EC</t>
+          <t>Shrew mouse</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FA-13.1.5.2 Foods for special medical purposes, as defined by Regulation (EU) No 609/2013, intended for infants as from four months of age and for young children</t>
+          <t>Shrew mouse$Shrew</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A0C25</t>
+          <t>A040B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>implicitFacets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FA-13.1.5.1 Dietary foods for infants for special medical purposes and special formulae for infants</t>
+          <t>F04.A02QE$F04.A0BXT$F04.A0ETG$F04.A07XJ$F04.A006Q</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FA-13.1.5.1 Foods for special medical purposes, as defined by Regulation (EU) No 609/2013, intended for infants</t>
+          <t>F04.A02QE$F04.A0BXT$F04.A0ETG$F04.A006Q</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A0C26</t>
+          <t>A007A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>implicitFacets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FA-13.1.5 Dietary foods for infants and young children for special medical purposes as defined by Commission Directive 1999/21/EC ( 3 ) and special formulae for infants</t>
+          <t>F33.A0C3T</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FA-13.1.5 Foods for special medical purposes, as defined by Regulation (EU) No 609/2013, intended for infants and young children</t>
+          <t>F33.A0C3Y</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A0C28</t>
+          <t>A005T</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>implicitFacets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FA-13.1.3 Processed cereal-based foods and baby foods for infants and young children as defined by Commission Directive 2006/125/EC ( 2 )</t>
+          <t>F10.A06HR$F33.A0C21$F10.A0B8L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FA-13.1.3 Processed cereal-based foods and baby foods as defined by Regulation (EU) No 609/2013</t>
+          <t>F10.A06HR$F10.A0B8L</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A0C29</t>
+          <t>A03RK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>implicitFacets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FA-13.1.2 Follow-on formulae as defined by Directive 2006/141/EC</t>
+          <t>F33.A0C27$F10.A07VP$F23.A07TF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FA-13.1.2 Follow-on formulae as defined by Regulation (EU) No 609/2013</t>
+          <t>F10.A07VP$F23.A07TF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A0C2A</t>
+          <t>A03RP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>implicitFacets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FA-13.1.1 Infant formulae as defined by Commission Directive 2006/141/EC ( 1 )</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FA-13.1.1 Infant formulae as defined by Regulation (EU) No 609/2013</t>
-        </is>
-      </c>
+          <t>F33.A0C27</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A0C2C</t>
+          <t>A005S</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>implicitFacets</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FA-13. Foods intended for particular nutritional uses as defined by Directive 2009/ 39/EC</t>
+          <t>F10.A07XK$F33.A0C21$F10.A0B8L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FA-13. Foods intended for specific groups as defined by Regulation (EU) No 609/2013</t>
+          <t>F10.A07XK$F10.A0B8L</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A0CRX</t>
+          <t>A00EK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>ScopeNote</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mole (as animal)</t>
+          <t>The group includes any type of Muesli plain, which is based only on cereals (i.e. without other major ingredients). The part consumed/analysed is by default the whole or a portion of it representing the observed heterogeneity.£https://www.google.co.uk/search?tbm=isch&amp;q=Muesli+plain</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Talpidae (as animal)</t>
+          <t>The group includes any type of Muesli plain, which is based only on cereals (i.e. without other major ingredients). When the term is accompanied by baking facet descriptors, it can be used to code granola. The part consumed/analysed is by default the whole or a portion of it representing the observed heterogeneity.£https://www.google.co.uk/search?tbm=isch&amp;q=Muesli+plain</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A0CRX</t>
+          <t>A0C22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Live animal of the taxonomic family Talpidae (Eulipotyphla order). The animals are commonly known as Mole. The part considered is by default the whole living animal.£https://en.wikipedia.org/wiki/Talpidae</t>
+          <t>FA-13.3 Dietary foods for weight control diets intended to replace total daily food intake or an individual meal (the whole or part of the total daily diet)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Live animal of the taxonomic family Talpidae (Eulipotyphla order). The animals are commonly known as Moles. The part considered is by default the whole living animal.£https://en.wikipedia.org/wiki/Talpidae</t>
+          <t>FA-13.3 Total diet replacement for weight control food as defined by Regulation (EU) No 609/2013</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A16CG</t>
+          <t>A0C23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1854,12 +1792,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bats (as animal)</t>
+          <t>FA-13.2 Dietary foods for special medical purposes defined in Directive 1999/21/EC (excluding products from food category 13.1.5)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chiroptera (as animal)</t>
+          <t>FA-13.2 Foods for special medical purposes as defined by Regulation (EU) No 609/2013 (excluding products from food category 13.1.5)</t>
         </is>
       </c>
     </row>
@@ -1888,44 +1826,666 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A16EA</t>
+          <t>A16DD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Shrew (as animal)</t>
-        </is>
-      </c>
+          <t>commonNames</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Soricidae (as animal)</t>
+          <t>Hedgehog</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A16EA</t>
+          <t>A0C13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Live animal of the taxonomic subfamilies Crocidurinae, Myosoricinae and Soricinae (in Soricidae family and in Eulipotyphla order). The animals are commonly known as Shrew or Shrew mouse (which is not a rodent and not a mole). The part considered is by default the whole living animal.£https://en.wikipedia.org/wiki/Shrew</t>
+          <t>FA-18. Processed foods not covered by categories 1 to 17, excluding foods for infants and young children</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Live animal of the taxonomic family Soricidae (Eulipotyphla order). The animals are commonly known as Shrew or Shrew mouse (which is not a rodent and not a mole). The part considered is by default the whole living animal.£https://en.wikipedia.org/wiki/Shrew</t>
+          <t>FA-18. Processed foods not covered by categories 1 to 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A03RF</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>F04.A0EYH$F33.A0C27$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>F04.A0EYH$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A0CRX</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mole (as animal)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Talpidae (as animal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A0CRX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ScopeNote</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Live animal of the taxonomic family Talpidae (Eulipotyphla order). The animals are commonly known as Mole. The part considered is by default the whole living animal.£https://en.wikipedia.org/wiki/Talpidae</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Live animal of the taxonomic family Talpidae (Eulipotyphla order). The animals are commonly known as Moles. The part considered is by default the whole living animal.£https://en.wikipedia.org/wiki/Talpidae</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A0CRX</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>commonNames</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Moles</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A03RH</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>F04.A0BXZ$F33.A0C27$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>F04.A0BXZ$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A16GS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>F23.A07TF$F28.A07KG$F33.A0C27</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>F23.A07TF$F28.A07KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A03RD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>F04.A07XJ$F33.A0C27$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>F04.A07XJ$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A00LM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>F01.A05DY$F02.A067K$F27.A00LM$F33.A0C51</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>F01.A058Y$F02.A067K$F27.A00LM$F33.A0C51</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A16CG</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bats (as animal)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Chiroptera (as animal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A16CG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>commonNames</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bats</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A003N</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>F10.A0B8L$F33.A0C21$F03.A06JD$F27.A001K$F28.A0C0A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>F10.A0B8L$F03.A06JD$F27.A001K$F28.A0C0A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A03HH</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>F03.A06JD$F04.A03HF$F28.A07KG$F28.A07LA$F33.A0C4F</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>F03.A06JD$F33.A0C1T$F04.A03HF$F28.A07KG$F28.A07LA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A008B</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>F10.A0B8L$F33.A0C21</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>F10.A0B8L</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A03RC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>F02.A06FL$F10.A07VP$F23.A07TF$F33.A0C27</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>F02.A06FL$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A004N</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>F10.A0B8L$F33.A0C21$F27.A001M$F28.A0C0B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>F10.A0B8L$F27.A001M$F28.A0C0B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A03RM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>F03.A06JL$F23.A07TF$F33.A0C27</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>F03.A06JL$F23.A07TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A00EL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ScopeNote</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>The group includes any type of Mixed breakfast cereals, including mixed muesli, usually made by cereal grains mixed with other ingredients, like raisins, chocolate, nuts and dried fruit. All the characterising ingredients should be reported with additional facet descriptors. The part consumed/analysed is by default the whole or a portion of it representing the observed heterogeneity.£https://www.google.co.uk/search?tbm=isch&amp;q=muesli with mixed ingredients</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>The group includes any type of Mixed breakfast cereals, including mixed muesli, usually made by cereal grains mixed with other ingredients, like raisins, chocolate, nuts and dried fruit. All the characterising ingredients should be reported with additional facet descriptors. Also, when the term is accompanied by baking facet descriptors, it can be used to code granola. The part consumed/analysed is by default the whole or a portion of it representing the observed heterogeneity.£https://www.google.co.uk/search?tbm=isch&amp;q=muesli with mixed ingredients</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A03RG</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>F04.A026V$F33.A0C27$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>F04.A026V$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A0C26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FA-13.1.5 Dietary foods for infants and young children for special medical purposes as defined by Commission Directive 1999/21/EC ( 3 ) and special formulae for infants</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FA-13.1.5 Foods for special medical purposes, as defined by Regulation (EU) No 609/2013, intended for infants and young children</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A00MB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Radish leaves</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Large radish leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A00MB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ScopeNote</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Leaves from the plant classified under the species Raphanus sativus L., commonly known as Radish leaves. The part consumed/analysed is not specified. When relevant, information on the part consumed/analysed has to be reported with additional facet descriptors. In case of data collections related to legislations, the default part consumed/analysed is the one defined in the applicable legislation.£https://en.wikipedia.org/wiki/Raphanus_sativus£https://www.google.co.uk/search?tbm=isch&amp;q=Radish+leaves+</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Leaves from the plant classified under the species Raphanus sativus L., commonly known as Large radish leaves. The part consumed/analysed is not specified. When relevant, information on the part consumed/analysed has to be reported with additional facet descriptors. In case of data collections related to legislations, the default part consumed/analysed is the one defined in the applicable legislation.£https://en.wikipedia.org/wiki/Raphanus_sativus£https://www.google.co.uk/search?tbm=isch&amp;q=Radish+leaves+</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A03RN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>F23.A07TF$F33.A0C27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>F23.A07TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A02KC</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ScopeNote</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>The group includes any type of Fish fingers, breaded. The part consumed/analysed is by default the whole, or a portion representing the heterogeneity observed in the product. When relevant, information on the part consumed/analysed has to be reported with additional facet descriptors.£https://en.wikipedia.org/wiki/Fish_fingers£https://www.google.co.uk/search?tbm=isch&amp;q=Fish fingers, breaded</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>The group includes any type of Fish fingers, breaded, including fish fillet. The part consumed/analysed is by default the whole, or a portion representing the heterogeneity observed in the product. When relevant, information on the part consumed/analysed has to be reported with additional facet descriptors.£https://en.wikipedia.org/wiki/Fish_fingers£https://www.google.co.uk/search?tbm=isch&amp;q=Fish fingers, breaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A0C28</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FA-13.1.3 Processed cereal-based foods and baby foods for infants and young children as defined by Commission Directive 2006/125/EC ( 2 )</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FA-13.1.3 Processed cereal-based foods and baby foods as defined by Regulation (EU) No 609/2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A18FY</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>commonNames</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ginger powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A03RJ</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>F04.A04RK$F33.A0C27$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>F04.A04RK$F10.A07VP$F23.A07TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A005R</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>implicitFacets</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>F10.A0B8L$F33.A0C21</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>F10.A0B8L</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A0C29</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FA-13.1.2 Follow-on formulae as defined by Directive 2006/141/EC</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>FA-13.1.2 Follow-on formulae as defined by Regulation (EU) No 609/2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A0C25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FA-13.1.5.1 Dietary foods for infants for special medical purposes and special formulae for infants</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FA-13.1.5.1 Foods for special medical purposes, as defined by Regulation (EU) No 609/2013, intended for infants</t>
         </is>
       </c>
     </row>
